--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484785_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484785_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>15.0922</v>
+        <v>14.9575</v>
       </c>
       <c r="E2" t="n">
-        <v>9.5684</v>
+        <v>9.724600000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>5.5238</v>
+        <v>5.2328</v>
       </c>
       <c r="G2" t="n">
         <v>9.1736</v>
@@ -610,13 +610,13 @@
         <v>3.2079</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2393</v>
+        <v>0.1045</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3839</v>
+        <v>-0.2277</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6232</v>
+        <v>0.3322</v>
       </c>
       <c r="V2" t="n">
         <v>2.4714</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>10.0184</v>
+        <v>7.6032</v>
       </c>
       <c r="E3" t="n">
-        <v>5.715</v>
+        <v>3.9612</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3034</v>
+        <v>3.642</v>
       </c>
       <c r="G3" t="n">
         <v>4.3929</v>
@@ -688,13 +688,13 @@
         <v>1.5096</v>
       </c>
       <c r="S3" t="n">
-        <v>4.4747</v>
+        <v>2.0596</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9198</v>
+        <v>1.1659</v>
       </c>
       <c r="U3" t="n">
-        <v>1.555</v>
+        <v>0.8935999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>0.5846</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. BEDIA FERRER</t>
+          <t>F. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1955</v>
+        <v>6.3942</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6742</v>
+        <v>1.7491</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5213</v>
+        <v>4.6451</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3916</v>
+        <v>5.1546</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6812</v>
+        <v>2.0809</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7104</v>
+        <v>3.0737</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3269</v>
+        <v>3.5374</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5043</v>
+        <v>1.6114</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8226</v>
+        <v>1.9261</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0647</v>
+        <v>1.6172</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1769</v>
+        <v>0.4696</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8878</v>
+        <v>1.1476</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3774</v>
+        <v>1.5096</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.8305</v>
+        <v>-1.887</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2079</v>
+        <v>3.3966</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4455</v>
+        <v>0.0318</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1968</v>
+        <v>0.0987</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2487</v>
+        <v>-0.0669</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.019</v>
+        <v>-0.3018</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.019</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. GOMEZ CARBONELL</t>
+          <t>J. BEDIA FERRER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>6.0838</v>
+        <v>5.7407</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3594</v>
+        <v>1.2458</v>
       </c>
       <c r="F5" t="n">
-        <v>4.7244</v>
+        <v>4.4949</v>
       </c>
       <c r="G5" t="n">
-        <v>5.1546</v>
+        <v>4.3916</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0809</v>
+        <v>2.6812</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0737</v>
+        <v>1.7104</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5374</v>
+        <v>3.3269</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6114</v>
+        <v>2.5043</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9261</v>
+        <v>0.8226</v>
       </c>
       <c r="M5" t="n">
-        <v>1.6172</v>
+        <v>1.0647</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4696</v>
+        <v>0.1769</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1476</v>
+        <v>0.8878</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5096</v>
+        <v>0.3774</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.887</v>
+        <v>-2.8305</v>
       </c>
       <c r="R5" t="n">
-        <v>3.3966</v>
+        <v>3.2079</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2786</v>
+        <v>0.9907</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.291</v>
+        <v>0.7684</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0124</v>
+        <v>0.2223</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3018</v>
+        <v>-0.019</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.019</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2015</v>
+        <v>3.8198</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.3825</v>
+        <v>-1.4468</v>
       </c>
       <c r="F6" t="n">
-        <v>5.584</v>
+        <v>5.2665</v>
       </c>
       <c r="G6" t="n">
         <v>2.0421</v>
@@ -922,13 +922,13 @@
         <v>3.3966</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3691</v>
+        <v>0.2491</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9747</v>
+        <v>-0.039</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6056</v>
+        <v>0.2881</v>
       </c>
       <c r="V6" t="n">
         <v>0.019</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.8778</v>
+        <v>3.081</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6266</v>
+        <v>0.724</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2512</v>
+        <v>2.357</v>
       </c>
       <c r="G7" t="n">
         <v>1.4762</v>
@@ -1000,13 +1000,13 @@
         <v>1.887</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7789</v>
+        <v>0.9821</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3215</v>
+        <v>0.4189</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4574</v>
+        <v>0.5632</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3208</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2753</v>
+        <v>3.0329</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0813</v>
+        <v>-0.5354</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3567</v>
+        <v>3.5683</v>
       </c>
       <c r="G8" t="n">
         <v>0.9136</v>
@@ -1078,13 +1078,13 @@
         <v>1.887</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3868</v>
+        <v>0.1591</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4402</v>
+        <v>-0.2286</v>
       </c>
       <c r="V8" t="n">
         <v>0.3018</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.2086</v>
+        <v>2.8893</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3099</v>
+        <v>0.6996</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8987</v>
+        <v>2.1897</v>
       </c>
       <c r="G9" t="n">
         <v>2.5896</v>
@@ -1156,13 +1156,13 @@
         <v>1.3209</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4186</v>
+        <v>0.2622</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2228</v>
+        <v>0.1669</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1957</v>
+        <v>0.0953</v>
       </c>
       <c r="V9" t="n">
         <v>0.6036</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2265</v>
+        <v>1.5943</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8736</v>
+        <v>-0.7174</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1001</v>
+        <v>2.3117</v>
       </c>
       <c r="G10" t="n">
         <v>1.1985</v>
@@ -1234,13 +1234,13 @@
         <v>0.9435</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6137</v>
+        <v>-0.2459</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7519</v>
+        <v>-0.5957</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1382</v>
+        <v>0.3498</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3018</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9982</v>
+        <v>1.3602</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5416</v>
+        <v>-0.4442</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5399</v>
+        <v>1.8044</v>
       </c>
       <c r="G11" t="n">
         <v>0.4663</v>
@@ -1312,13 +1312,13 @@
         <v>1.3209</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7889</v>
+        <v>-0.4269</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7055</v>
+        <v>-0.608</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0835</v>
+        <v>0.1811</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9495</v>
+        <v>-0.9508</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8256</v>
+        <v>-3.1179</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8761</v>
+        <v>2.1671</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5803</v>
@@ -1390,13 +1390,13 @@
         <v>1.5096</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9517</v>
+        <v>0.9504</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1474</v>
+        <v>0.8551</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1957</v>
+        <v>0.0953</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>49.2283</v>
+        <v>49.52229999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>11.5489</v>
+        <v>11.8426</v>
       </c>
       <c r="F13" t="n">
-        <v>37.6796</v>
+        <v>37.6795</v>
       </c>
       <c r="G13" t="n">
         <v>31.2187</v>
@@ -1468,10 +1468,10 @@
         <v>23.5875</v>
       </c>
       <c r="S13" t="n">
-        <v>4.594100000000001</v>
+        <v>4.888100000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8689</v>
+        <v>2.162599999999999</v>
       </c>
       <c r="U13" t="n">
         <v>2.7254</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3948</v>
+        <v>-0.2565</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3317</v>
+        <v>-0.4291</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0631</v>
+        <v>0.1727</v>
       </c>
       <c r="G15" t="n">
         <v>-0.718</v>
@@ -1624,13 +1624,13 @@
         <v>1.3209</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3751</v>
+        <v>-0.2368</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4086</v>
+        <v>-0.506</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0335</v>
+        <v>0.2693</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6226</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. ALFEREZ CANSECO</t>
+          <t>P. DIAZ MUNOZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.2654</v>
+        <v>-1.3859</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8549</v>
+        <v>-1.5351</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4105</v>
+        <v>0.1492</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2546</v>
+        <v>-0.6844</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4908</v>
+        <v>-0.5525</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2363</v>
+        <v>-0.1319</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1647</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2058</v>
+        <v>-0.6496</v>
       </c>
       <c r="L16" t="n">
         <v>0.0411</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0899</v>
+        <v>-0.076</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.285</v>
+        <v>0.097</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1951</v>
+        <v>-0.173</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3774</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5096</v>
+        <v>0.1887</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6684</v>
+        <v>0.0533</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1968</v>
+        <v>0.0169</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5284</v>
+        <v>0.0365</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. DIAZ MUNOZ</t>
+          <t>M. MARTIN MARTINEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3029</v>
+        <v>-1.8275</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2428</v>
+        <v>-0.5664</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0601</v>
+        <v>-1.2611</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6844</v>
+        <v>-1.0132</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5525</v>
+        <v>-1.1496</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1319</v>
+        <v>0.1364</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6084000000000001</v>
+        <v>0.4777</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6496</v>
+        <v>0.4281</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0411</v>
+        <v>0.0496</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.076</v>
+        <v>-1.4909</v>
       </c>
       <c r="N17" t="n">
-        <v>0.097</v>
+        <v>-1.5777</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.173</v>
+        <v>0.0868</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7548</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1887</v>
+        <v>0.7548</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1364</v>
+        <v>0.6387</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3092</v>
+        <v>0.5411</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1728</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. MARTIN MARTINEZ</t>
+          <t>C. CASTELLANOS MARTINEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9213</v>
+        <v>-2.2205</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3715</v>
+        <v>-0.9738</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5497</v>
+        <v>-1.2466</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0132</v>
+        <v>-0.8922</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1496</v>
+        <v>-0.6519</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1364</v>
+        <v>-0.2403</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4777</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4281</v>
+        <v>0.0477</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0496</v>
+        <v>0.0411</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4909</v>
+        <v>-0.981</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5777</v>
+        <v>-0.6996</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0868</v>
+        <v>-0.2814</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1322</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7548</v>
+        <v>0.3774</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5449000000000001</v>
+        <v>-0.1586</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7359</v>
+        <v>-0.1192</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.191</v>
+        <v>-0.0394</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3208</v>
+        <v>-0.6036</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6226</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. CASTELLANOS MARTINEZ</t>
+          <t>D. ALFEREZ CANSECO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6932</v>
+        <v>-2.2254</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2662</v>
+        <v>-2.0241</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4271</v>
+        <v>-0.2012</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8922</v>
+        <v>-1.2546</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6519</v>
+        <v>-1.4908</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2403</v>
+        <v>0.2363</v>
       </c>
       <c r="J19" t="n">
-        <v>0.08890000000000001</v>
+        <v>-0.1647</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0477</v>
+        <v>-0.2058</v>
       </c>
       <c r="L19" t="n">
         <v>0.0411</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.981</v>
+        <v>-1.0899</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6996</v>
+        <v>-1.285</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2814</v>
+        <v>0.1951</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5661</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3774</v>
+        <v>1.5096</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6313</v>
+        <v>-0.2916</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4115</v>
+        <v>0.0276</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2198</v>
+        <v>-0.3191</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6036</v>
+        <v>-0.3018</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6036</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1403</v>
+        <v>-2.6568</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8254</v>
+        <v>-2.6305</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3149</v>
+        <v>-0.0262</v>
       </c>
       <c r="G20" t="n">
         <v>-3.0108</v>
@@ -2014,13 +2014,13 @@
         <v>1.887</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0728</v>
+        <v>-0.5893</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3375</v>
+        <v>-0.1426</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7353</v>
+        <v>-0.4467</v>
       </c>
       <c r="V20" t="n">
         <v>0.9434</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.3051</v>
+        <v>-4.0309</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0144</v>
+        <v>-2.8196</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2907</v>
+        <v>-1.2113</v>
       </c>
       <c r="G21" t="n">
         <v>-2.106</v>
@@ -2092,13 +2092,13 @@
         <v>0.1887</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5009</v>
+        <v>-0.2266</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5879</v>
+        <v>-0.393</v>
       </c>
       <c r="U21" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.1664</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.195</v>
+        <v>-5.5612</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9494</v>
+        <v>-3.6571</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2456</v>
+        <v>-1.904</v>
       </c>
       <c r="G22" t="n">
         <v>-4.2331</v>
@@ -2170,13 +2170,13 @@
         <v>1.6983</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7924</v>
+        <v>-1.1585</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2222</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5702</v>
+        <v>-0.2286</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9244</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.8508</v>
+        <v>-5.8235</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5493</v>
+        <v>-4.9647</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3014</v>
+        <v>-0.8588</v>
       </c>
       <c r="G23" t="n">
         <v>-4.5141</v>
@@ -2248,13 +2248,13 @@
         <v>1.3209</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4497</v>
+        <v>-0.4224</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2222</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2274</v>
+        <v>0.2152</v>
       </c>
       <c r="V23" t="n">
         <v>0.6226</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.658</v>
+        <v>-8.4817</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.6461</v>
+        <v>-7.9384</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0119</v>
+        <v>-0.5434</v>
       </c>
       <c r="G24" t="n">
         <v>-6.3927</v>
@@ -2326,13 +2326,13 @@
         <v>1.6983</v>
       </c>
       <c r="S24" t="n">
-        <v>1.1122</v>
+        <v>0.2885</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1459</v>
+        <v>-0.4382</v>
       </c>
       <c r="U24" t="n">
-        <v>1.2581</v>
+        <v>0.7267</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3018</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-14.1186</v>
+        <v>-13.4269</v>
       </c>
       <c r="E25" t="n">
-        <v>-11.2448</v>
+        <v>-10.7576</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.8738</v>
+        <v>-2.6693</v>
       </c>
       <c r="G25" t="n">
         <v>-7.0166</v>
@@ -2404,13 +2404,13 @@
         <v>2.2644</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2339</v>
+        <v>-0.5421</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6314</v>
+        <v>-0.1443</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6024</v>
+        <v>-0.3979</v>
       </c>
       <c r="V25" t="n">
         <v>-1.528</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-49.2284</v>
+        <v>-47.27979999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-37.6795</v>
+        <v>-37.6794</v>
       </c>
       <c r="F26" t="n">
-        <v>-11.5488</v>
+        <v>-9.6</v>
       </c>
       <c r="G26" t="n">
         <v>-31.2187</v>
@@ -2482,13 +2482,13 @@
         <v>13.209</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.5942</v>
+        <v>-2.6454</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.7253</v>
+        <v>-2.7252</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.8687</v>
+        <v>0.07999999999999996</v>
       </c>
       <c r="V26" t="n">
         <v>-3.037</v>
